--- a/StructureDefinition-Signering-Deltagande.xlsx
+++ b/StructureDefinition-Signering-Deltagande.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Signering-Deltagande.xlsx
+++ b/StructureDefinition-Signering-Deltagande.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="95">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Signering : Deltagande).</t>
+    <t>Klassen Signering håller information om tidsangivelse då ett relaterat objekt är signerat.
+Inom laboratoriedomänen finns det fyra olika typer av signering. Signeringen avser hela laboratoriesvaret eller enskilda analyser.
+1. Laboratoriesvaret signeras av en medicinskt ansvarig hälso- och sjukvårdspersonal på den ansvariga enheten.
+Den ansvariga enheten kan vara den remissvarsmottagande enheten eller den utförande enheten (exempelvis vid patientnära analyser).
+2. En enskild analys signeras av den hälso- och sjukvårdspersonal som utför analysen.
+3. Laboratoriesvaret signeras av hälso- och sjukvårdspersonal på den remissvarsmottagande enheten när det förs in i patientjournalen.
+4. En enskild analys signeras av hälso- och sjukvårdspersonal på den remissvarsmottagande enheten när den förs in i patientjournalen.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -258,6 +264,9 @@
   </si>
   <si>
     <t>Source attribute: tidpunkt</t>
+  </si>
+  <si>
+    <t>Angivelse av tidpunkt då signering genomfördes.</t>
   </si>
   <si>
     <t>Signering-Deltagande.harMottgares</t>
@@ -885,7 +894,7 @@
         <v>80</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -953,10 +962,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -979,13 +988,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1036,7 +1045,7 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>73</v>
@@ -1053,10 +1062,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1079,13 +1088,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1136,7 +1145,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1153,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1179,13 +1188,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1236,7 +1245,7 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1253,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1279,13 +1288,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1336,7 +1345,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1353,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1379,13 +1388,13 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1436,7 +1445,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
